--- a/Stats Sheet/Round Gaps/Identification.xlsx
+++ b/Stats Sheet/Round Gaps/Identification.xlsx
@@ -748,7 +748,7 @@
     <x:t>silverteeth</x:t>
   </x:si>
   <x:si>
-    <x:t>tonylmao</x:t>
+    <x:t>Tonylmao</x:t>
   </x:si>
   <x:si>
     <x:t>turicake</x:t>
